--- a/results/Int Task Remove ACC -0.5/Rando_2_permute.xlsx
+++ b/results/Int Task Remove ACC -0.5/Rando_2_permute.xlsx
@@ -440,587 +440,587 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7174688253269308</v>
+        <v>0.720840055421641</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7253834911837835</v>
+        <v>0.7057325336420749</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7245436255622829</v>
+        <v>0.7012532503274052</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7248218725681856</v>
+        <v>0.7015922333782527</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7123402357317745</v>
+        <v>0.7017102890656139</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7135039003928862</v>
+        <v>0.7066027672860478</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7081391994230075</v>
+        <v>0.6896873991686754</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7081982272666882</v>
+        <v>0.6927095868050943</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7151077115797067</v>
+        <v>0.7032905650350181</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7180422115512366</v>
+        <v>0.6547265928976788</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7171433180860554</v>
+        <v>0.6603543568622241</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7202987454210716</v>
+        <v>0.6743993774555394</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7202987454210716</v>
+        <v>0.6810002467401826</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7229229221629624</v>
+        <v>0.6760774004972764</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7214337502609751</v>
+        <v>0.6695794028887582</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7196798071630574</v>
+        <v>0.6662047563915197</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7083904948089661</v>
+        <v>0.6628014500730731</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7063717805151176</v>
+        <v>0.6628014500730731</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7055015468711447</v>
+        <v>0.6574788847343747</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7010205553552109</v>
+        <v>0.6882369464953404</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7010205553552109</v>
+        <v>0.669269079659119</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7013595384060585</v>
+        <v>0.6762782090458747</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7047780287357412</v>
+        <v>0.697180518913584</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6894799476151612</v>
+        <v>0.6989817222464745</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6795313834532237</v>
+        <v>0.6936559303053884</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6774384573044584</v>
+        <v>0.6747860003416403</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6816681534344335</v>
+        <v>0.6408759276481865</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.715741833848957</v>
+        <v>0.6545398295594739</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7386881014291951</v>
+        <v>0.6573107218099341</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7290498604968967</v>
+        <v>0.6185926319585476</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7063531801013532</v>
+        <v>0.6028864805359956</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7073566534439235</v>
+        <v>0.6094452141894585</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6596224875206407</v>
+        <v>0.6057063412226925</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6599614705714882</v>
+        <v>0.6018831969935657</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6550824681610264</v>
+        <v>0.6019422248372464</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6295676352800501</v>
+        <v>0.6055850589329437</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5916725188376639</v>
+        <v>0.6033924877104409</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5925123844591645</v>
+        <v>0.6027145216087459</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5729155199574848</v>
+        <v>0.6080657467686527</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5747133068878471</v>
+        <v>0.6089056123901532</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5732545030083323</v>
+        <v>0.5967477745933532</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5739358855125553</v>
+        <v>0.5873490614383055</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5728160646838878</v>
+        <v>0.5876290166454723</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5005303015924232</v>
+        <v>0.589839998481599</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5105378935980412</v>
+        <v>0.5801966329455084</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5042911913754816</v>
+        <v>0.5733951449124073</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4758923453603355</v>
+        <v>0.5579586994894377</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4879254844648585</v>
+        <v>0.5979418072769374</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4921703646060698</v>
+        <v>0.5663962647332359</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5049843414884126</v>
+        <v>0.5636422646952759</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5053233245392601</v>
+        <v>0.5608713724448156</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5215068233150493</v>
+        <v>0.5608713724448156</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5215068233150493</v>
+        <v>0.5625966557215252</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5483337445669709</v>
+        <v>0.5405644656177045</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5964894566021979</v>
+        <v>0.5433370660694289</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.556730882380853</v>
+        <v>0.5266562909256552</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5399960141970506</v>
+        <v>0.5029646781938618</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5408966158634958</v>
+        <v>0.5142556987492171</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5344426518875623</v>
+        <v>0.5197232713952208</v>
       </c>
     </row>
     <row r="61">
@@ -1030,297 +1030,297 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5628718659251808</v>
+        <v>0.5103870024863818</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5623119555108471</v>
+        <v>0.5094004213563118</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5233391538709738</v>
+        <v>0.5059077191717122</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5224402604057927</v>
+        <v>0.5052297530700173</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.516281245848122</v>
+        <v>0.5034033063184467</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5179609770911231</v>
+        <v>0.503241406798641</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5132607664129671</v>
+        <v>0.5010017651413062</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5143805872416346</v>
+        <v>0.5007218099341394</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5184770436730123</v>
+        <v>0.5013407481921537</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5212765957446809</v>
+        <v>0.5013407481921537</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5223964165733482</v>
+        <v>0.5009427372976256</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5223964165733482</v>
+        <v>0.5009427372976256</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.54081443240268</v>
+        <v>0.5002647711959307</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5228972991440014</v>
+        <v>0.4989830508474576</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5205075255755689</v>
+        <v>0.498924023003777</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5173993584755253</v>
+        <v>0.498924023003777</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5133029020441475</v>
+        <v>0.4985850399529296</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5138931804809536</v>
+        <v>0.4982460569020821</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5155442519027464</v>
+        <v>0.4995429612617914</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5154852240590658</v>
+        <v>0.4992039782109439</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.51551217567901</v>
+        <v>0.4992039782109439</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5031586539374039</v>
+        <v>0.4992039782109439</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5031586539374039</v>
+        <v>0.4961531307533168</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5085115872985746</v>
+        <v>0.4940011767608708</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5159758574221345</v>
+        <v>0.4945762711864407</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5182627593144419</v>
+        <v>0.4942372881355932</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5072029153301574</v>
+        <v>0.4979661016949152</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5083531041812971</v>
+        <v>0.4989830508474576</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5079095412530605</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5010017651413062</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
